--- a/exports/BAJFINANCE_full_report.xlsx
+++ b/exports/BAJFINANCE_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q73"/>
+  <dimension ref="A1:U73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>5.89</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44579.55208333334</v>
+        <v>44580.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>777</v>
+        <v>757</v>
       </c>
       <c r="I2" t="n">
         <v>757.0707290348225</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K2" t="n">
-        <v>0.39</v>
+        <v>-2.2</v>
       </c>
       <c r="L2" t="n">
-        <v>2.2</v>
+        <v>3.42</v>
       </c>
       <c r="M2" t="n">
         <v>0.45</v>
       </c>
       <c r="N2" t="n">
-        <v>1.02</v>
+        <v>2.32</v>
       </c>
       <c r="O2" t="n">
         <v>0.72</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,25 +626,25 @@
         <v>8.69</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44629.55208333334</v>
+        <v>44630.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>648.5</v>
+        <v>667</v>
       </c>
       <c r="I3" t="n">
         <v>663.7926394262736</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>50</v>
       </c>
       <c r="K3" t="n">
-        <v>14.33</v>
+        <v>11.89</v>
       </c>
       <c r="L3" t="n">
         <v>6.27</v>
       </c>
       <c r="M3" t="n">
-        <v>2.95</v>
+        <v>4.78</v>
       </c>
       <c r="N3" t="n">
         <v>5.84</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>8.880000000000001</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44670.55208333334</v>
+        <v>44671.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>720</v>
+        <v>709</v>
       </c>
       <c r="I4" t="n">
         <v>713.56781953145</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K4" t="n">
-        <v>7.95</v>
+        <v>6.3</v>
       </c>
       <c r="L4" t="n">
         <v>2.7</v>
@@ -669,7 +716,7 @@
         <v>0.68</v>
       </c>
       <c r="N4" t="n">
-        <v>1.57</v>
+        <v>2.08</v>
       </c>
       <c r="O4" t="n">
         <v>1.46</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>6.33</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44708.55208333334</v>
+        <v>44711.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>598</v>
+        <v>611.5</v>
       </c>
       <c r="I5" t="n">
         <v>607.9356529998279</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>40</v>
       </c>
       <c r="K5" t="n">
-        <v>15.66</v>
+        <v>13.75</v>
       </c>
       <c r="L5" t="n">
         <v>2.89</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>6.96</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44721.55208333334</v>
+        <v>44722.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>590</v>
+        <v>569</v>
       </c>
       <c r="I6" t="n">
         <v>581.2950249454381</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.52</v>
+        <v>-6.95</v>
       </c>
       <c r="L6" t="n">
-        <v>5.15</v>
+        <v>7.44</v>
       </c>
       <c r="M6" t="n">
-        <v>0.66</v>
+        <v>1.27</v>
       </c>
       <c r="N6" t="n">
-        <v>2.49</v>
+        <v>4.07</v>
       </c>
       <c r="O6" t="n">
         <v>2.26</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>7.22</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44746.55208333334</v>
+        <v>44747.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>563</v>
+        <v>575</v>
       </c>
       <c r="I7" t="n">
         <v>569.5276596626834</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K7" t="n">
-        <v>1.05</v>
+        <v>-1.05</v>
       </c>
       <c r="L7" t="n">
         <v>2.55</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>6.7</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44792.55208333334</v>
+        <v>44795.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>729</v>
+        <v>716</v>
       </c>
       <c r="I8" t="n">
         <v>719.7897730850449</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>45.16666666666666</v>
+        <v>48</v>
       </c>
       <c r="K8" t="n">
-        <v>26.78</v>
+        <v>24.52</v>
       </c>
       <c r="L8" t="n">
         <v>2.09</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>6</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44803.38541666666</v>
+        <v>44803.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="I9" t="n">
         <v>729.4169477628166</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.84</v>
+        <v>-1.96</v>
       </c>
       <c r="L9" t="n">
-        <v>1.68</v>
+        <v>2.37</v>
       </c>
       <c r="M9" t="n">
         <v>1.06</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>5.42</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44830.38541666666</v>
+        <v>44830.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>734</v>
+        <v>726</v>
       </c>
       <c r="I10" t="n">
         <v>732.3794779595332</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>26.83333333333333</v>
+        <v>27</v>
       </c>
       <c r="K10" t="n">
-        <v>0.55</v>
+        <v>-0.55</v>
       </c>
       <c r="L10" t="n">
         <v>3.15</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>6.89</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44924.55208333334</v>
+        <v>44925.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>651</v>
+        <v>667.5</v>
       </c>
       <c r="I11" t="n">
         <v>664.5876363952883</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>94</v>
+        <v>94.83333333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>10.33</v>
+        <v>8.06</v>
       </c>
       <c r="L11" t="n">
         <v>4.68</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>130</v>
+        <v>131</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>5.28</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44930.55208333334</v>
+        <v>44931.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>656</v>
+        <v>608</v>
       </c>
       <c r="I12" t="n">
         <v>632.6825115310318</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.72</v>
+        <v>-8.91</v>
       </c>
       <c r="L12" t="n">
-        <v>2.85</v>
+        <v>9.66</v>
       </c>
       <c r="M12" t="n">
-        <v>0.23</v>
+        <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>0.61</v>
+        <v>7.01</v>
       </c>
       <c r="O12" t="n">
         <v>1.08</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>9.69</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44953.55208333334</v>
+        <v>44956.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>577</v>
+        <v>597.5</v>
       </c>
       <c r="I13" t="n">
         <v>596.8164484865214</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K13" t="n">
-        <v>5.1</v>
+        <v>1.73</v>
       </c>
       <c r="L13" t="n">
         <v>6.74</v>
@@ -1182,7 +1337,7 @@
         <v>0.58</v>
       </c>
       <c r="N13" t="n">
-        <v>1.36</v>
+        <v>4.33</v>
       </c>
       <c r="O13" t="n">
         <v>-7.01</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>5.96</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44958.55208333334</v>
+        <v>44959.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>583.5</v>
+        <v>568</v>
       </c>
       <c r="I14" t="n">
         <v>569.3486767259177</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.34</v>
+        <v>-4.94</v>
       </c>
       <c r="L14" t="n">
-        <v>4.27</v>
+        <v>5.52</v>
       </c>
       <c r="M14" t="n">
         <v>1.25</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>7.37</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44963.38541666666</v>
+        <v>44963.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="I15" t="n">
         <v>605.3373582001254</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K15" t="n">
-        <v>-6.16</v>
+        <v>-7.57</v>
       </c>
       <c r="L15" t="n">
-        <v>6.34</v>
+        <v>7.83</v>
       </c>
       <c r="M15" t="n">
         <v>1.05</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>6.56</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44981.55208333334</v>
+        <v>44984.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>622.5</v>
+        <v>614</v>
       </c>
       <c r="I16" t="n">
         <v>618.7100562170029</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>18</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K16" t="n">
-        <v>1.88</v>
+        <v>0.49</v>
       </c>
       <c r="L16" t="n">
         <v>1.47</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>4.85</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45006.55208333334</v>
+        <v>45007.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>571</v>
+        <v>584</v>
       </c>
       <c r="I17" t="n">
         <v>580.6078616339781</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K17" t="n">
-        <v>7</v>
+        <v>4.89</v>
       </c>
       <c r="L17" t="n">
         <v>1.79</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>5.68</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45013.38541666666</v>
+        <v>45013.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>558</v>
+        <v>554.5</v>
       </c>
       <c r="I18" t="n">
         <v>556.522544155377</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K18" t="n">
-        <v>-4.45</v>
+        <v>-5.05</v>
       </c>
       <c r="L18" t="n">
-        <v>4.71</v>
+        <v>5.39</v>
       </c>
       <c r="M18" t="n">
         <v>0.43</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>5.07</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45021.55208333334</v>
+        <v>45022.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>576</v>
+        <v>592.5</v>
       </c>
       <c r="I19" t="n">
         <v>582.6226321115223</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.88</v>
+        <v>-6.85</v>
       </c>
       <c r="L19" t="n">
         <v>7.3</v>
@@ -1524,7 +1751,7 @@
         <v>2.01</v>
       </c>
       <c r="N19" t="n">
-        <v>1.71</v>
+        <v>3.3</v>
       </c>
       <c r="O19" t="n">
         <v>-0.98</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>7.2</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45098.55208333334</v>
+        <v>45099.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>720.5</v>
+        <v>708</v>
       </c>
       <c r="I20" t="n">
         <v>712.6066074296511</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>76.16666666666667</v>
+        <v>77</v>
       </c>
       <c r="K20" t="n">
-        <v>21.6</v>
+        <v>19.49</v>
       </c>
       <c r="L20" t="n">
         <v>3.71</v>
@@ -1581,7 +1820,7 @@
         <v>0.3</v>
       </c>
       <c r="N20" t="n">
-        <v>2.02</v>
+        <v>2.29</v>
       </c>
       <c r="O20" t="n">
         <v>3.3</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>104</v>
+        <v>105</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>4.35</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45107.55208333334</v>
+        <v>45110.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>716</v>
+        <v>727</v>
       </c>
       <c r="I21" t="n">
         <v>722.9525877243012</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.13</v>
+        <v>-2.68</v>
       </c>
       <c r="L21" t="n">
-        <v>1.77</v>
+        <v>2.82</v>
       </c>
       <c r="M21" t="n">
         <v>0.36</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>2.51</v>
       </c>
       <c r="O21" t="n">
         <v>-2.29</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>4.02</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45118.38541666666</v>
+        <v>45118.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="I22" t="n">
         <v>749.3397313756323</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K22" t="n">
-        <v>3.16</v>
+        <v>2.34</v>
       </c>
       <c r="L22" t="n">
         <v>1.51</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>5.13</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45161.38541666666</v>
+        <v>45161.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="I23" t="n">
         <v>710.8089702662913</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>42.83333333333334</v>
+        <v>43</v>
       </c>
       <c r="K23" t="n">
-        <v>4.57</v>
+        <v>4.3</v>
       </c>
       <c r="L23" t="n">
         <v>3.97</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>3.66</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45218.38541666666</v>
+        <v>45218.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>789</v>
+        <v>782</v>
       </c>
       <c r="I24" t="n">
         <v>783.9981209974756</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>56.83333333333334</v>
+        <v>57</v>
       </c>
       <c r="K24" t="n">
-        <v>10.81</v>
+        <v>9.83</v>
       </c>
       <c r="L24" t="n">
         <v>0.49</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>4.45</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45261.55208333334</v>
+        <v>45264.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>725</v>
+        <v>740</v>
       </c>
       <c r="I25" t="n">
         <v>730.5342760041081</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>43</v>
+        <v>45.83333333333334</v>
       </c>
       <c r="K25" t="n">
-        <v>7.29</v>
+        <v>5.37</v>
       </c>
       <c r="L25" t="n">
         <v>1.02</v>
@@ -1866,7 +2165,7 @@
         <v>1.35</v>
       </c>
       <c r="N25" t="n">
-        <v>2.09</v>
+        <v>2.21</v>
       </c>
       <c r="O25" t="n">
         <v>-0.45</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>4.02</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45281.38541666666</v>
+        <v>45281.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>746</v>
+        <v>738.5</v>
       </c>
       <c r="I26" t="n">
         <v>741.5494890843823</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K26" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.2</v>
       </c>
       <c r="L26" t="n">
         <v>2.57</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>3.79</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45294.55208333334</v>
+        <v>45295.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>738</v>
+        <v>766.5</v>
       </c>
       <c r="I27" t="n">
         <v>746.6655709993561</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K27" t="n">
-        <v>0.07000000000000001</v>
+        <v>-3.79</v>
       </c>
       <c r="L27" t="n">
-        <v>1.35</v>
+        <v>4.6</v>
       </c>
       <c r="M27" t="n">
-        <v>0.63</v>
+        <v>2.44</v>
       </c>
       <c r="N27" t="n">
-        <v>1.92</v>
+        <v>4.27</v>
       </c>
       <c r="O27" t="n">
         <v>-1.27</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>4.65</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45307.38541666666</v>
+        <v>45307.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>747</v>
+        <v>744.5</v>
       </c>
       <c r="I28" t="n">
         <v>745.3946758950137</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K28" t="n">
-        <v>-2.54</v>
+        <v>-2.87</v>
       </c>
       <c r="L28" t="n">
         <v>3.07</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>4.94</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45369.55208333334</v>
+        <v>45370.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>650</v>
+        <v>660</v>
       </c>
       <c r="I29" t="n">
         <v>659.9816744430626</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>62</v>
+        <v>62.83333333333334</v>
       </c>
       <c r="K29" t="n">
-        <v>12.69</v>
+        <v>11.35</v>
       </c>
       <c r="L29" t="n">
         <v>1.01</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>5.68</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45397.55208333334</v>
+        <v>45398.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>707</v>
+        <v>694</v>
       </c>
       <c r="I30" t="n">
         <v>700.1772593577931</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K30" t="n">
-        <v>7.12</v>
+        <v>5.15</v>
       </c>
       <c r="L30" t="n">
         <v>1.44</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,25 +2558,25 @@
         <v>4.65</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45401.55208333334</v>
+        <v>45404.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>710.5</v>
+        <v>724.5</v>
       </c>
       <c r="I31" t="n">
         <v>717.5245359192161</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.38</v>
+        <v>-4.39</v>
       </c>
       <c r="L31" t="n">
-        <v>3.03</v>
+        <v>5.19</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="N31" t="n">
         <v>3.05</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>5.02</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45407.55208333334</v>
+        <v>45408.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>729.5</v>
+        <v>670</v>
       </c>
       <c r="I32" t="n">
         <v>700.1677658565559</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K32" t="n">
-        <v>0.6899999999999999</v>
+        <v>-7.52</v>
       </c>
       <c r="L32" t="n">
-        <v>1.66</v>
+        <v>7.66</v>
       </c>
       <c r="M32" t="n">
-        <v>-0</v>
+        <v>4.04</v>
       </c>
       <c r="N32" t="n">
-        <v>0.82</v>
+        <v>7.75</v>
       </c>
       <c r="O32" t="n">
         <v>2.74</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>9.630000000000001</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45443.55208333334</v>
+        <v>45446.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>673</v>
+        <v>694</v>
       </c>
       <c r="I33" t="n">
         <v>688.5983146464429</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.45</v>
+        <v>-3.58</v>
       </c>
       <c r="L33" t="n">
         <v>10.45</v>
@@ -2322,7 +2717,7 @@
         <v>6.31</v>
       </c>
       <c r="N33" t="n">
-        <v>1.51</v>
+        <v>2.82</v>
       </c>
       <c r="O33" t="n">
         <v>-7.75</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>4.97</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>692</v>
+        <v>659</v>
       </c>
       <c r="I34" t="n">
         <v>662.4286957604688</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.29</v>
+        <v>-5.04</v>
       </c>
       <c r="L34" t="n">
-        <v>1.59</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M34" t="n">
-        <v>-0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="O34" t="n">
         <v>2.82</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,25 +2834,25 @@
         <v>7.35</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45449.55208333334</v>
+        <v>45450.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>692.5</v>
+        <v>720</v>
       </c>
       <c r="I35" t="n">
         <v>705.4677564340202</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K35" t="n">
-        <v>-5.08</v>
+        <v>-9.26</v>
       </c>
       <c r="L35" t="n">
-        <v>6.37</v>
+        <v>10.77</v>
       </c>
       <c r="M35" t="n">
-        <v>0.84</v>
+        <v>1.01</v>
       </c>
       <c r="N35" t="n">
         <v>4.35</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>8.279999999999999</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45483.55208333334</v>
+        <v>45484.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>704.5</v>
+        <v>696.5</v>
       </c>
       <c r="I36" t="n">
         <v>704.1160737136244</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K36" t="n">
-        <v>-2.15</v>
+        <v>-3.26</v>
       </c>
       <c r="L36" t="n">
-        <v>3.61</v>
+        <v>3.75</v>
       </c>
       <c r="M36" t="n">
         <v>0.63</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>4.59</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45523.55208333334</v>
+        <v>45524.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>662</v>
+        <v>672</v>
       </c>
       <c r="I37" t="n">
         <v>669.5100494689963</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>40</v>
       </c>
       <c r="K37" t="n">
-        <v>4.95</v>
+        <v>3.52</v>
       </c>
       <c r="L37" t="n">
         <v>2.23</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>4.17</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45568.38541666666</v>
+        <v>45568.55208333334</v>
       </c>
       <c r="H38" t="n">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="I38" t="n">
         <v>745.1648091002156</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>44</v>
+        <v>44.16666666666666</v>
       </c>
       <c r="K38" t="n">
-        <v>11.01</v>
+        <v>10.57</v>
       </c>
       <c r="L38" t="n">
         <v>1.49</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>4.79</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45587.55208333334</v>
+        <v>45588.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>664.5</v>
+        <v>706</v>
       </c>
       <c r="I39" t="n">
         <v>703.859876923183</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K39" t="n">
-        <v>10.57</v>
+        <v>4.98</v>
       </c>
       <c r="L39" t="n">
         <v>0.54</v>
@@ -2664,7 +3131,7 @@
         <v>0.59</v>
       </c>
       <c r="N39" t="n">
-        <v>1.32</v>
+        <v>5.42</v>
       </c>
       <c r="O39" t="n">
         <v>-3.76</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>9.35</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45607.55208333334</v>
+        <v>45608.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>676.5</v>
+        <v>664.5</v>
       </c>
       <c r="I40" t="n">
         <v>664.6503382602775</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K40" t="n">
-        <v>-4.18</v>
+        <v>-5.88</v>
       </c>
       <c r="L40" t="n">
         <v>6.52</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>6.49</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45630.55208333334</v>
+        <v>45631.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>673.5</v>
+        <v>682.5</v>
       </c>
       <c r="I41" t="n">
         <v>674.6886302097327</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K41" t="n">
-        <v>-1.35</v>
+        <v>-2.71</v>
       </c>
       <c r="L41" t="n">
         <v>3.24</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>5.06</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45644.55208333334</v>
+        <v>45645.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>707</v>
+        <v>690</v>
       </c>
       <c r="I42" t="n">
         <v>692.9487688134238</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K42" t="n">
-        <v>3.59</v>
+        <v>1.1</v>
       </c>
       <c r="L42" t="n">
         <v>2.05</v>
       </c>
       <c r="M42" t="n">
-        <v>0.21</v>
+        <v>1.7</v>
       </c>
       <c r="N42" t="n">
-        <v>1.05</v>
+        <v>2.19</v>
       </c>
       <c r="O42" t="n">
         <v>1.71</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>5.22</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45658.55208333334</v>
+        <v>45659.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>694</v>
+        <v>736</v>
       </c>
       <c r="I43" t="n">
         <v>707.6931663794589</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.58</v>
+        <v>-6.67</v>
       </c>
       <c r="L43" t="n">
-        <v>1.81</v>
+        <v>6.67</v>
       </c>
       <c r="M43" t="n">
         <v>1.02</v>
       </c>
       <c r="N43" t="n">
-        <v>1.54</v>
+        <v>6.2</v>
       </c>
       <c r="O43" t="n">
         <v>-2.19</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>7.46</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45721.38541666666</v>
+        <v>45721.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="I44" t="n">
         <v>833.0403208117019</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>62</v>
+        <v>62.16666666666666</v>
       </c>
       <c r="K44" t="n">
-        <v>13.45</v>
+        <v>12.77</v>
       </c>
       <c r="L44" t="n">
         <v>5.3</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>5.32</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45734.38541666666</v>
+        <v>45734.55208333334</v>
       </c>
       <c r="H45" t="n">
-        <v>867</v>
+        <v>869.5</v>
       </c>
       <c r="I45" t="n">
         <v>869.1279701005604</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>12.83333333333333</v>
+        <v>13</v>
       </c>
       <c r="K45" t="n">
-        <v>-4.46</v>
+        <v>-4.76</v>
       </c>
       <c r="L45" t="n">
-        <v>4.52</v>
+        <v>4.82</v>
       </c>
       <c r="M45" t="n">
         <v>0.78</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>4.69</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45748.55208333334</v>
+        <v>45750.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>872</v>
+        <v>858</v>
       </c>
       <c r="I46" t="n">
         <v>864.6718982094364</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>14</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K46" t="n">
-        <v>0.29</v>
+        <v>-1.32</v>
       </c>
       <c r="L46" t="n">
-        <v>1.78</v>
+        <v>2.7</v>
       </c>
       <c r="M46" t="n">
         <v>1.68</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,25 +3662,25 @@
         <v>6.06</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45758.55208333334</v>
+        <v>45762.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>892</v>
+        <v>915</v>
       </c>
       <c r="I47" t="n">
         <v>897.8406346422205</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K47" t="n">
-        <v>-3.96</v>
+        <v>-6.64</v>
       </c>
       <c r="L47" t="n">
-        <v>4.55</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="M47" t="n">
-        <v>0.99</v>
+        <v>3.76</v>
       </c>
       <c r="N47" t="n">
         <v>2.74</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>5.85</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45776.55208333334</v>
+        <v>45777.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>910.5</v>
+        <v>861.5</v>
       </c>
       <c r="I48" t="n">
         <v>895.237678377226</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.49</v>
+        <v>-5.85</v>
       </c>
       <c r="L48" t="n">
-        <v>2.19</v>
+        <v>6.5</v>
       </c>
       <c r="M48" t="n">
-        <v>0.28</v>
+        <v>2.91</v>
       </c>
       <c r="N48" t="n">
-        <v>2.21</v>
+        <v>5.44</v>
       </c>
       <c r="O48" t="n">
         <v>2.47</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>7.94</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45791.55208333334</v>
+        <v>45792.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>907.5</v>
+        <v>913</v>
       </c>
       <c r="I49" t="n">
         <v>909.2879940319021</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K49" t="n">
-        <v>-5.34</v>
+        <v>-5.98</v>
       </c>
       <c r="L49" t="n">
-        <v>6.33</v>
+        <v>6.79</v>
       </c>
       <c r="M49" t="n">
         <v>2.19</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>4.75</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45812.55208333334</v>
+        <v>45813.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>899.5</v>
+        <v>893</v>
       </c>
       <c r="I50" t="n">
         <v>896.2082977509633</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K50" t="n">
-        <v>-1.48</v>
+        <v>-2.19</v>
       </c>
       <c r="L50" t="n">
-        <v>1.81</v>
+        <v>2.85</v>
       </c>
       <c r="M50" t="n">
         <v>0.43</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>3.05</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45813.55208333334</v>
+        <v>45814.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>893</v>
+        <v>941</v>
       </c>
       <c r="I51" t="n">
         <v>918.7271696446619</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>-5.38</v>
       </c>
       <c r="L51" t="n">
-        <v>0.67</v>
+        <v>5.66</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="O51" t="n">
         <v>-0.72</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>6.96</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45826.55208333334</v>
+        <v>45827.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>919</v>
+        <v>903.5</v>
       </c>
       <c r="I52" t="n">
         <v>918.6322039961373</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K52" t="n">
-        <v>-2.34</v>
+        <v>-3.99</v>
       </c>
       <c r="L52" t="n">
         <v>5.69</v>
@@ -3405,7 +4028,7 @@
         <v>2.35</v>
       </c>
       <c r="N52" t="n">
-        <v>1.55</v>
+        <v>2.34</v>
       </c>
       <c r="O52" t="n">
         <v>4.93</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>5.81</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45833.55208333334</v>
+        <v>45834.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>927.5</v>
+        <v>948.5</v>
       </c>
       <c r="I53" t="n">
         <v>938.0558887731916</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K53" t="n">
-        <v>-2.66</v>
+        <v>-4.98</v>
       </c>
       <c r="L53" t="n">
-        <v>3.6</v>
+        <v>5.53</v>
       </c>
       <c r="M53" t="n">
         <v>0.77</v>
       </c>
       <c r="N53" t="n">
-        <v>1.22</v>
+        <v>2.48</v>
       </c>
       <c r="O53" t="n">
         <v>-2.34</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>5.62</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45862.55208333334</v>
+        <v>45863.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>956.4</v>
+        <v>915.6</v>
       </c>
       <c r="I54" t="n">
         <v>929.221507717902</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K54" t="n">
-        <v>0.83</v>
+        <v>-3.47</v>
       </c>
       <c r="L54" t="n">
-        <v>4.57</v>
+        <v>5.32</v>
       </c>
       <c r="M54" t="n">
-        <v>0.86</v>
+        <v>5.23</v>
       </c>
       <c r="N54" t="n">
-        <v>1.63</v>
+        <v>4.55</v>
       </c>
       <c r="O54" t="n">
         <v>2.48</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>4.98</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45883.55208333334</v>
+        <v>45887.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>862</v>
+        <v>914.9</v>
       </c>
       <c r="I55" t="n">
         <v>893.3757799929086</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K55" t="n">
-        <v>5.85</v>
+        <v>0.08</v>
       </c>
       <c r="L55" t="n">
         <v>1.02</v>
       </c>
       <c r="M55" t="n">
-        <v>0.55</v>
+        <v>1.51</v>
       </c>
       <c r="N55" t="n">
-        <v>1.14</v>
+        <v>4.99</v>
       </c>
       <c r="O55" t="n">
         <v>-4.55</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>7.35</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45926.38541666666</v>
+        <v>45926.55208333334</v>
       </c>
       <c r="H56" t="n">
-        <v>997.6</v>
+        <v>985</v>
       </c>
       <c r="I56" t="n">
         <v>992.4173112455517</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>39</v>
+        <v>39.16666666666666</v>
       </c>
       <c r="K56" t="n">
-        <v>9.039999999999999</v>
+        <v>7.66</v>
       </c>
       <c r="L56" t="n">
         <v>4.94</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>4.71</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45937.55208333334</v>
+        <v>45938.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>1018</v>
+        <v>1027.55</v>
       </c>
       <c r="I57" t="n">
         <v>1023.944393643291</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>11</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K57" t="n">
-        <v>-3.35</v>
+        <v>-4.32</v>
       </c>
       <c r="L57" t="n">
         <v>4.52</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>4.92</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45959.55208333334</v>
+        <v>45960.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>1063.8</v>
+        <v>1048.25</v>
       </c>
       <c r="I58" t="n">
         <v>1051.818998754302</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K58" t="n">
-        <v>3.53</v>
+        <v>2.01</v>
       </c>
       <c r="L58" t="n">
         <v>1.58</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>5.01</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45971.38541666666</v>
+        <v>45971.55208333334</v>
       </c>
       <c r="H59" t="n">
-        <v>1076.7</v>
+        <v>1084.2</v>
       </c>
       <c r="I59" t="n">
         <v>1083.640737677841</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K59" t="n">
-        <v>-2.71</v>
+        <v>-3.43</v>
       </c>
       <c r="L59" t="n">
-        <v>3.27</v>
+        <v>3.79</v>
       </c>
       <c r="M59" t="n">
         <v>0.05</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>4.85</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45971.55208333334</v>
+        <v>45972.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>1084.2</v>
+        <v>1003</v>
       </c>
       <c r="I60" t="n">
         <v>1031.62215493113</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>-7.49</v>
       </c>
       <c r="L60" t="n">
-        <v>0.8100000000000001</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="M60" t="n">
-        <v>-0</v>
+        <v>3.74</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="O60" t="n">
         <v>1.36</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>8.83</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45987.55208333334</v>
+        <v>45988.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>1011</v>
+        <v>1041.9</v>
       </c>
       <c r="I61" t="n">
         <v>1025.368109922315</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.8</v>
+        <v>-3.88</v>
       </c>
       <c r="L61" t="n">
-        <v>4.06</v>
+        <v>4.18</v>
       </c>
       <c r="M61" t="n">
         <v>0.91</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>5.71</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46001.55208333334</v>
+        <v>46002.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>1009.6</v>
+        <v>1002.7</v>
       </c>
       <c r="I62" t="n">
         <v>1008.755249504333</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K62" t="n">
-        <v>-3.1</v>
+        <v>-3.76</v>
       </c>
       <c r="L62" t="n">
-        <v>3.32</v>
+        <v>4.01</v>
       </c>
       <c r="M62" t="n">
         <v>0.54</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>4.96</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46055.55208333334</v>
+        <v>46056.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>908</v>
+        <v>961.15</v>
       </c>
       <c r="I63" t="n">
         <v>945.9932376797428</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>53.16666666666666</v>
+        <v>54</v>
       </c>
       <c r="K63" t="n">
-        <v>9.44</v>
+        <v>4.14</v>
       </c>
       <c r="L63" t="n">
         <v>3.46</v>
       </c>
       <c r="M63" t="n">
-        <v>1.18</v>
+        <v>5.73</v>
       </c>
       <c r="N63" t="n">
-        <v>1.92</v>
+        <v>6.17</v>
       </c>
       <c r="O63" t="n">
         <v>-0.12</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>7.15</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46080.55208333334</v>
+        <v>46083.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>996.5</v>
+        <v>972.7</v>
       </c>
       <c r="I64" t="n">
         <v>989.6088456281341</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K64" t="n">
-        <v>3.68</v>
+        <v>1.2</v>
       </c>
       <c r="L64" t="n">
         <v>2</v>
       </c>
       <c r="M64" t="n">
-        <v>0.67</v>
+        <v>2.56</v>
       </c>
       <c r="N64" t="n">
-        <v>1.74</v>
+        <v>2.16</v>
       </c>
       <c r="O64" t="n">
         <v>6.17</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>5.83</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46105.55208333334</v>
+        <v>46106.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>852</v>
+        <v>880.15</v>
       </c>
       <c r="I65" t="n">
         <v>870.4936073834564</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K65" t="n">
-        <v>12.41</v>
+        <v>9.51</v>
       </c>
       <c r="L65" t="n">
         <v>1.82</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>9.19</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46108.55208333334</v>
+        <v>46111.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>846.5</v>
+        <v>811.2</v>
       </c>
       <c r="I66" t="n">
         <v>818.4236492761429</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K66" t="n">
-        <v>-3.82</v>
+        <v>-7.83</v>
       </c>
       <c r="L66" t="n">
-        <v>4.42</v>
+        <v>8.31</v>
       </c>
       <c r="M66" t="n">
-        <v>0.7</v>
+        <v>1.83</v>
       </c>
       <c r="N66" t="n">
-        <v>3.93</v>
+        <v>5.26</v>
       </c>
       <c r="O66" t="n">
         <v>3.42</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>9.91</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>854</v>
+        <v>916</v>
       </c>
       <c r="I67" t="n">
         <v>872.5851162099227</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K67" t="n">
-        <v>-5.28</v>
+        <v>-12.92</v>
       </c>
       <c r="L67" t="n">
-        <v>6.36</v>
+        <v>14.15</v>
       </c>
       <c r="M67" t="n">
-        <v>3.84</v>
+        <v>4.22</v>
       </c>
       <c r="N67" t="n">
-        <v>2.62</v>
+        <v>7.38</v>
       </c>
       <c r="O67" t="n">
         <v>-5.26</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>9.91</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46153.55208333334</v>
+        <v>46154.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>935.5</v>
+        <v>911.15</v>
       </c>
       <c r="I68" t="n">
         <v>924.4676966854074</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K68" t="n">
-        <v>2.13</v>
+        <v>-0.53</v>
       </c>
       <c r="L68" t="n">
         <v>3.82</v>
@@ -4317,7 +5132,7 @@
         <v>2.91</v>
       </c>
       <c r="N68" t="n">
-        <v>2.76</v>
+        <v>3.05</v>
       </c>
       <c r="O68" t="n">
         <v>7.38</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>7.01</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46185.38541666666</v>
+        <v>46185.55208333334</v>
       </c>
       <c r="H69" t="n">
-        <v>889.1</v>
+        <v>920</v>
       </c>
       <c r="I69" t="n">
         <v>913.8561433286527</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>31</v>
+        <v>31.16666666666667</v>
       </c>
       <c r="K69" t="n">
-        <v>2.42</v>
+        <v>-0.97</v>
       </c>
       <c r="L69" t="n">
         <v>4.09</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>7.09</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46226.55208333334</v>
+        <v>46227.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>1040</v>
+        <v>1013.9</v>
       </c>
       <c r="I70" t="n">
         <v>1025.055876812294</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>41</v>
+        <v>41.83333333333334</v>
       </c>
       <c r="K70" t="n">
-        <v>13.04</v>
+        <v>10.21</v>
       </c>
       <c r="L70" t="n">
         <v>3.53</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,28 +5318,28 @@
         <v>4.97</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46233.55208333334</v>
+        <v>46234.38541666666</v>
       </c>
       <c r="H71" t="n">
-        <v>1057</v>
+        <v>1143.4</v>
       </c>
       <c r="I71" t="n">
         <v>1060.841944470998</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K71" t="n">
-        <v>-4.25</v>
+        <v>-12.77</v>
       </c>
       <c r="L71" t="n">
-        <v>5.34</v>
+        <v>12.79</v>
       </c>
       <c r="M71" t="n">
-        <v>0.8100000000000001</v>
+        <v>3.6</v>
       </c>
       <c r="N71" t="n">
-        <v>2.94</v>
+        <v>7.95</v>
       </c>
       <c r="O71" t="n">
         <v>-2.07</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,28 +5387,28 @@
         <v>8.81</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46240.55208333334</v>
+        <v>46241.38541666666</v>
       </c>
       <c r="H72" t="n">
-        <v>1152</v>
+        <v>1083.5</v>
       </c>
       <c r="I72" t="n">
         <v>1095.443541680772</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K72" t="n">
-        <v>0.75</v>
+        <v>-5.24</v>
       </c>
       <c r="L72" t="n">
-        <v>5.23</v>
+        <v>5.37</v>
       </c>
       <c r="M72" t="n">
-        <v>-0</v>
+        <v>3.39</v>
       </c>
       <c r="N72" t="n">
-        <v>0.11</v>
+        <v>6.16</v>
       </c>
       <c r="O72" t="n">
         <v>7.95</v>
@@ -4554,7 +5417,19 @@
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4605,6 +5480,14 @@
       <c r="Q73" t="n">
         <v>110</v>
       </c>
+      <c r="R73" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6707,7 +7590,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.4</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="6">
@@ -6717,7 +7600,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="7">
@@ -6727,7 +7610,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>94</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="8">
@@ -6737,7 +7620,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="9">
@@ -6747,7 +7630,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33.2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10">
@@ -6757,7 +7640,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>45.2</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11">
@@ -6797,7 +7680,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.53</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="15">
@@ -6807,7 +7690,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.07</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="16">
@@ -6817,7 +7700,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.97</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -6827,7 +7710,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>26.78</v>
+        <v>24.52</v>
       </c>
     </row>
     <row r="18">
@@ -6837,7 +7720,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>53.5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6847,7 +7730,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.38</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="20">
@@ -6857,7 +7740,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.15</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="21">
@@ -6867,7 +7750,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10.45</v>
+        <v>14.15</v>
       </c>
     </row>
     <row r="22">
@@ -6877,7 +7760,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23">
@@ -6887,7 +7770,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -6897,7 +7780,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.11</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="25">
@@ -6917,7 +7800,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.42</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="27">
@@ -6927,7 +7810,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5.84</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="28">
@@ -6937,7 +7820,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29">
